--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel 02/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel 02/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.94311</v>
+        <v>16.99781</v>
       </c>
       <c r="D2" t="n">
-        <v>16.75008</v>
+        <v>16.28838</v>
       </c>
       <c r="E2" t="n">
-        <v>16.7599</v>
+        <v>16.52776</v>
       </c>
       <c r="F2" t="n">
-        <v>43.10336</v>
+        <v>42.03905</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05068</v>
+        <v>0.05098</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84941</v>
+        <v>1.82956</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.59988</v>
+        <v>16.92739</v>
       </c>
       <c r="D3" t="n">
-        <v>16.49425</v>
+        <v>16.42428</v>
       </c>
       <c r="E3" t="n">
-        <v>16.29017</v>
+        <v>16.88611</v>
       </c>
       <c r="F3" t="n">
-        <v>43.16964</v>
+        <v>43.33101</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0516</v>
+        <v>0.0511</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83202</v>
+        <v>1.82874</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.83325</v>
+        <v>17.10609</v>
       </c>
       <c r="D4" t="n">
-        <v>16.8159</v>
+        <v>16.37087</v>
       </c>
       <c r="E4" t="n">
-        <v>16.73511</v>
+        <v>16.88131</v>
       </c>
       <c r="F4" t="n">
-        <v>42.25216</v>
+        <v>42.514</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04963</v>
+        <v>0.0501</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83078</v>
+        <v>1.8429</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.382</v>
+        <v>16.90929</v>
       </c>
       <c r="D6" t="n">
-        <v>15.91337</v>
+        <v>16.08543</v>
       </c>
       <c r="E6" t="n">
-        <v>16.02364</v>
+        <v>16.18</v>
       </c>
       <c r="F6" t="n">
-        <v>21.20432</v>
+        <v>21.52385</v>
       </c>
       <c r="G6" t="n">
-        <v>34.0979</v>
+        <v>33.88117</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.71773</v>
+        <v>16.6814</v>
       </c>
       <c r="D7" t="n">
-        <v>15.81493</v>
+        <v>16.00251</v>
       </c>
       <c r="E7" t="n">
-        <v>16.22505</v>
+        <v>16.66397</v>
       </c>
       <c r="F7" t="n">
-        <v>21.56744</v>
+        <v>21.68085</v>
       </c>
       <c r="G7" t="n">
-        <v>33.74778</v>
+        <v>34.01438</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.82194</v>
+        <v>16.46675</v>
       </c>
       <c r="D8" t="n">
-        <v>15.82631</v>
+        <v>16.41848</v>
       </c>
       <c r="E8" t="n">
-        <v>16.45482</v>
+        <v>16.44651</v>
       </c>
       <c r="F8" t="n">
-        <v>21.78774</v>
+        <v>21.82466</v>
       </c>
       <c r="G8" t="n">
-        <v>34.60484</v>
+        <v>33.92207</v>
       </c>
     </row>
   </sheetData>
